--- a/tame_output/ON/bt/strategyON_20231127.xlsx
+++ b/tame_output/ON/bt/strategyON_20231127.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>91.0%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>22.1%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,16 +911,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.8%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,16 +1064,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1217,16 +1217,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.5%</t>
+          <t>131.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.4%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>27.7%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1793"/>
+  <dimension ref="A1:G1794"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.156246943390047</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42765,6 +42765,29 @@
       </c>
       <c r="G1793" t="n">
         <v>4.377057361206851</v>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" s="2" t="n">
+        <v>45256</v>
+      </c>
+      <c r="B1794" t="n">
+        <v>3.145119495204679</v>
+      </c>
+      <c r="C1794" t="n">
+        <v>3.076099785321473</v>
+      </c>
+      <c r="D1794" t="n">
+        <v>1.563178158774383</v>
+      </c>
+      <c r="E1794" t="n">
+        <v>3.701014624517479</v>
+      </c>
+      <c r="F1794" t="n">
+        <v>2.185473803765169</v>
+      </c>
+      <c r="G1794" t="n">
+        <v>4.387384067580576</v>
       </c>
     </row>
   </sheetData>
